--- a/output/2026-09-01_21_Italia_Marche_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-01_21_Italia_Marche_ATEX_Equipment-Services.xlsx
@@ -494,10 +494,9 @@
           <t>0733 203205 (sede Macerata); filiali non riverificate: 071 2132011 (Ancona), 0732 252611 (Fabriano), 0731 648811 (Jesi)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore materiale elettrico/illuminazione/automazione industriale; P.IVA 01634070435, REA MC. Nessuna linea ATEX dedicata pubblicizzata ma categoria merceologica coerente con fornitura componenti ATEX su richiesta.</t>
+          <t>Distributore materiale elettrico/illuminazione/automazione industriale; P.IVA 01634070435, REA MC. Nessuna linea ATEX dedicata pubblicizzata ma categoria merceologica coerente con fornitura componenti ATEX su richiesta. [DUPLICATO — vedi anche: 2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,7 +531,6 @@
           <t>0721 202242</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Componenti/ricambi automazione industriale (sensori, cuscinetti, oleodinamica); P.IVA 02525590416. Nessuna conferma esplicita di linea ATEX, ma gamma prodotti rende plausibile fornitura varianti ATEX su richiesta.</t>
